--- a/TestCase/Nhom_9_Unit_Test.xlsx
+++ b/TestCase/Nhom_9_Unit_Test.xlsx
@@ -598,14 +598,14 @@
   <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
